--- a/Parts_List/ESC Holder - DigiKey Order Form.xlsx
+++ b/Parts_List/ESC Holder - DigiKey Order Form.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lexha\Downloads\Ruka's ROV Folder\ESC Holder Final Version\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8437ba7af042dc6/Pictures/Screenshots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6938086-00A0-4321-B359-DD1A37CCC997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2AD47F2-0C01-4C13-A415-FAEF7459BE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E57E92EF-1CBE-EB40-BA08-924CF36E9605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>DigiKey</t>
   </si>
@@ -165,36 +165,6 @@
   </si>
   <si>
     <t>SUM:</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Part number</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/NAOEVO-Silicone-Electrical-Breadboard-Automotive/dp/B0CMLFRQDQ/ref=sr_1_1_sspa?crid=28HFCA73M1NJG&amp;dib=eyJ2IjoiMSJ9.xTXx3mvDP33NtIWhTjGjSeCk92IxD1sH_szoiohjMxebo2r5lg7IZ0eFMMlw8aN10lf3ojG1vi3BdVcFk94-68WApCGhoIfGuG-8XhZDg63R8og03CE4MeScFn0rsMRTC9475Joj_YaIfHDFOy7JP5hKC6d1Q-OQjPNwbKWOGZBLGDg2nEGuQL-yOMQVU15pTw49yMyQ_wl78ppoIdddkZK2lw6UYRpbqSjWVAKkBylUvRx-pO-AnqYL4Vj3n9QgzHlQwkZOnrNh4GV76QFQ96IqxcSoLLVQSxvnC5YQ-fs.s2tOPWEPgeZ7w-8Qe_OOWGqRUpcqmpvVtfD8IQqetYE&amp;dib_tag=se&amp;keywords=flexible+wire+18+awg&amp;qid=1761533539&amp;sprefix=flexible+wire+1+awg,aps,198&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAOEVO 16 Gauge Wire 60ft, 16 AWG Wire 6 Colors 10ft Each Spool, Flexible Silicone Tinned Copper Electrical Cable, Wiring kit for Breadboard/Automotive/DIY/Battery, 200℃ </t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Treela-Soldering-Pneumatic-Dispensing-Electronics/dp/B0BX62ZKJ2/ref=sxin_16_pa_sp_search_thematic_sspa?content-id=amzn1.sym.3566f435-7f05-435d-8f15-1289ee1fea99%3Aamzn1.sym.3566f435-7f05-435d-8f15-1289ee1fea99&amp;crid=1ZSTX0MOC5BLN&amp;cv_ct_cx=solder+flux&amp;keywords=solder+flux&amp;pd_rd_i=B0BX62ZKJ2&amp;pd_rd_r=2beda764-a11b-4f32-8102-23929d5657ca&amp;pd_rd_w=TDKmD&amp;pd_rd_wg=a7gSu&amp;pf_rd_p=3566f435-7f05-435d-8f15-1289ee1fea99&amp;pf_rd_r=1MG15W413TGMG40HWF8Z&amp;qid=1761534965&amp;s=hi&amp;sbo=RZvfv%2F%2FHxDF+O5021pAnSA==&amp;sprefix=solder+flux,tools,191&amp;sr=1-4-e169343e-09af-4d41-85b1-8335fe8f32d0-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9zZWFyY2hfdGhlbWF0aWM&amp;psc=1</t>
-  </si>
-  <si>
-    <t>Treela 4 Set 8341 No Clean Solder Flux Paste 10cc Tacky Solder Flux Syringe 40ml Pneumatic Dispenser with Plunger and Dispensing Tip for Electronics Soldering PCB IC Cellphone CPU LED Bga Repairing</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/XHF-Mounts-Adhesive-Organizer-Holders/dp/B083416L5L/ref=sr_1_3?crid=1X8E337ROL6PB&amp;dib=eyJ2IjoiMSJ9.RYHvy64GKxp7YrDguhCmrR9baf64RylwPq-WgiN7Iqj-tbVAFUvS9AsYIDJEAsj1fhfEbj54AEy4XxPzHxHSdI4RpMi8QHTzLIDCYnrRJT_-YbEiyKTY6WuQbKsHK8ose4VN6_YsP_rKQv19XRj6svF8TBRYb3FBboqleDKRZrCYA-W8Kh59LD2Ky8d1H24wfk13NwezPZrRQzz-I2P-MBwhodyU7prvFissVYhAOO4.xR1BTbrn1NCDZnGIptE79S1SqugWMKduYC6ucAedKfo&amp;dib_tag=se&amp;keywords=zip%2Btie%2Bmounts%2Bsmall&amp;qid=1761540678&amp;sprefix=zip%2Btie%2Bmounts%2Bsmall%2Caps%2C199&amp;sr=8-3&amp;th=1</t>
-  </si>
-  <si>
-    <t>XHF 200 PCS 1/2" Black Self Adhesive Cable Zip Tie Mounts Wire Cable Clips Holders Management Anchors Organizer Holders Squares(HS-100) Visit the XHF Storea</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/4-Port-USB-HUB-HAT-Compatible/dp/B083KMNR36/ref=sr_1_5?crid=3LSBZKQJGBTIP&amp;dib=eyJ2IjoiMSJ9.fEg-lGSBiJpgfcxDRbBTpQdJ_3jtoWXBIajbsQZLAA03nxysln5Sfkmnp1b0dJtO59zHncoXRBKtNnYBwnAArZgmO1MTjGTkySzII-4KlP6A-OmpHKOpLzMuHm793HA-FRQEd70EbTayJFq3Gf7qcGP8JGk2fZuaX9tpjLjJBEjpAPkp0Jqm2lYvm0cGxfPwuGysaAaw_WoXdIMoHB8es8ku1uCTlUSQNpIM8ZvNvo4.pb7rhezwGKaeM0av06D0orYSbXCe3RprGqsU5BtpyMk&amp;dib_tag=se&amp;keywords=usb+hub+rasp+pi+4&amp;qid=1761541969&amp;sprefix=usb+hub+rasp+pi+%2Caps%2C149&amp;sr=8-5</t>
-  </si>
-  <si>
-    <t>4-Port Raspberry Pi USB HUB HAT for Raspberry Pi 4B/3B+/3B/2B/B+/A+/Zero/Zero W, 4 USB Ports Compatible with USB2.0/1.1 Onboard USB to UART Onboard Multi</t>
   </si>
 </sst>
 </file>
@@ -548,7 +518,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -678,19 +648,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -738,15 +695,13 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="43" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="43" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="43" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -759,7 +714,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1154,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465A6CFE-22D4-5142-A977-9E9A4672E630}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="8.08203125" bestFit="1" customWidth="1"/>
@@ -1191,7 +1145,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="b">
+      <c r="A3" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B3" s="1">
@@ -1215,7 +1169,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="13" t="b">
+      <c r="A4" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B4" s="1">
@@ -1239,7 +1193,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="b">
+      <c r="A5" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B5" s="1">
@@ -1263,7 +1217,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="b">
+      <c r="A6" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B6" s="1">
@@ -1287,7 +1241,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" s="13" t="b">
+      <c r="A7" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B7" s="1">
@@ -1311,7 +1265,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" s="13" t="b">
+      <c r="A8" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B8" s="1">
@@ -1335,7 +1289,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" s="13" t="b">
+      <c r="A9" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B9" s="1">
@@ -1359,7 +1313,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" s="13" t="b">
+      <c r="A10" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B10" s="1">
@@ -1383,7 +1337,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" s="13" t="b">
+      <c r="A11" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B11" s="1">
@@ -1407,7 +1361,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" s="13" t="b">
+      <c r="A12" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B12" s="1">
@@ -1431,7 +1385,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" s="13" t="b">
+      <c r="A13" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B13" s="1">
@@ -1455,19 +1409,19 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A14" s="13" t="b">
+      <c r="A14" s="11" t="b">
         <v>0</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="3">
@@ -1479,13 +1433,13 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C15" s="11"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="9" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="7">
         <f>SUM(G3:G14)</f>
         <v>182.26</v>
       </c>
@@ -1493,127 +1447,9 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B17" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A19" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="B19" s="6">
-        <v>1</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="14">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="G19" s="14">
-        <f>F19*B19</f>
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A20" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="3">
-        <v>9.99</v>
-      </c>
-      <c r="G20" s="3">
-        <f>F20*B20</f>
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A21" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="3">
-        <v>9.99</v>
-      </c>
-      <c r="G21" s="3">
-        <f>F21*B21</f>
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A22" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" s="3">
-        <v>16.309999999999999</v>
-      </c>
-      <c r="G22" s="3">
-        <f>F22*B22</f>
-        <v>16.309999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="F23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="5">
-        <f>SUM(G19:G22)</f>
-        <v>53.28</v>
-      </c>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F17" s="7"/>
+      <c r="G17" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1627,11 +1463,8 @@
     <hyperlink ref="D11" r:id="rId8" xr:uid="{4FC24AFF-C049-074F-83EE-9AB0C77588D6}"/>
     <hyperlink ref="D12" r:id="rId9" xr:uid="{F300F57D-F00F-E445-9765-34187E414869}"/>
     <hyperlink ref="D13" r:id="rId10" xr:uid="{3C036E4B-18A4-E34A-B2C4-5142B27939A1}"/>
-    <hyperlink ref="D19" r:id="rId11" display="https://www.amazon.com/NAOEVO-Silicone-Electrical-Breadboard-Automotive/dp/B0CMLFRQDQ/ref=sr_1_1_sspa?crid=28HFCA73M1NJG&amp;dib=eyJ2IjoiMSJ9.xTXx3mvDP33NtIWhTjGjSeCk92IxD1sH_szoiohjMxebo2r5lg7IZ0eFMMlw8aN10lf3ojG1vi3BdVcFk94-68WApCGhoIfGuG-8XhZDg63R8og03CE4MeScFn0rsMRTC9475Joj_YaIfHDFOy7JP5hKC6d1Q-OQjPNwbKWOGZBLGDg2nEGuQL-yOMQVU15pTw49yMyQ_wl78ppoIdddkZK2lw6UYRpbqSjWVAKkBylUvRx-pO-AnqYL4Vj3n9QgzHlQwkZOnrNh4GV76QFQ96IqxcSoLLVQSxvnC5YQ-fs.s2tOPWEPgeZ7w-8Qe_OOWGqRUpcqmpvVtfD8IQqetYE&amp;dib_tag=se&amp;keywords=flexible+wire+18+awg&amp;qid=1761533539&amp;sprefix=flexible+wire+1+awg,aps,198&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{917E4AFE-3FDD-9F44-A976-AD270F5DB5F4}"/>
-    <hyperlink ref="D20" r:id="rId12" display="https://www.amazon.com/Treela-Soldering-Pneumatic-Dispensing-Electronics/dp/B0BX62ZKJ2/ref=sxin_16_pa_sp_search_thematic_sspa?content-id=amzn1.sym.3566f435-7f05-435d-8f15-1289ee1fea99%3Aamzn1.sym.3566f435-7f05-435d-8f15-1289ee1fea99&amp;crid=1ZSTX0MOC5BLN&amp;cv_ct_cx=solder+flux&amp;keywords=solder+flux&amp;pd_rd_i=B0BX62ZKJ2&amp;pd_rd_r=2beda764-a11b-4f32-8102-23929d5657ca&amp;pd_rd_w=TDKmD&amp;pd_rd_wg=a7gSu&amp;pf_rd_p=3566f435-7f05-435d-8f15-1289ee1fea99&amp;pf_rd_r=1MG15W413TGMG40HWF8Z&amp;qid=1761534965&amp;s=hi&amp;sbo=RZvfv%2F%2FHxDF+O5021pAnSA==&amp;sprefix=solder+flux,tools,191&amp;sr=1-4-e169343e-09af-4d41-85b1-8335fe8f32d0-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9zZWFyY2hfdGhlbWF0aWM&amp;psc=1" xr:uid="{2A69ED82-1AD1-A34C-A9E2-1F61AAD2C430}"/>
-    <hyperlink ref="D21" r:id="rId13" display="https://www.amazon.com/XHF-Mounts-Adhesive-Organizer-Holders/dp/B083416L5L/ref=sr_1_3?crid=1X8E337ROL6PB&amp;dib=eyJ2IjoiMSJ9.RYHvy64GKxp7YrDguhCmrR9baf64RylwPq-WgiN7Iqj-tbVAFUvS9AsYIDJEAsj1fhfEbj54AEy4XxPzHxHSdI4RpMi8QHTzLIDCYnrRJT_-YbEiyKTY6WuQbKsHK8ose4VN6_YsP_rKQv19XRj6svF8TBRYb3FBboqleDKRZrCYA-W8Kh59LD2Ky8d1H24wfk13NwezPZrRQzz-I2P-MBwhodyU7prvFissVYhAOO4.xR1BTbrn1NCDZnGIptE79S1SqugWMKduYC6ucAedKfo&amp;dib_tag=se&amp;keywords=zip%2Btie%2Bmounts%2Bsmall&amp;qid=1761540678&amp;sprefix=zip%2Btie%2Bmounts%2Bsmall%2Caps%2C199&amp;sr=8-3&amp;th=1" xr:uid="{23EC8C94-F2BB-5945-9400-478EF0FB44CE}"/>
-    <hyperlink ref="D14" r:id="rId14" xr:uid="{17AB69FE-9FA3-474C-B2CE-FD90D918C85C}"/>
-    <hyperlink ref="D3" r:id="rId15" xr:uid="{090708C7-0462-4A16-8AD5-73C4DBC6E740}"/>
+    <hyperlink ref="D14" r:id="rId11" xr:uid="{17AB69FE-9FA3-474C-B2CE-FD90D918C85C}"/>
+    <hyperlink ref="D3" r:id="rId12" xr:uid="{090708C7-0462-4A16-8AD5-73C4DBC6E740}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
